--- a/Current TAPPs/Solution_SF-ICP-MS_TAPP_v69.xlsx
+++ b/Current TAPPs/Solution_SF-ICP-MS_TAPP_v69.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legends" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legends" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +527,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
     <col width="4" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
@@ -583,7 +583,7 @@
           <t>Keyed By</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
@@ -717,7 +717,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="J3" s="1" t="n"/>
       <c r="K3" s="8" t="n"/>
       <c r="L3" s="1" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="1" t="n"/>
       <c r="K4" s="8" t="n"/>
       <c r="L4" s="1" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="1" t="n"/>
       <c r="K5" s="8" t="n"/>
       <c r="L5" s="1" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="1" t="n"/>
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="1" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="1" t="n"/>
       <c r="K7" s="8" t="n"/>
       <c r="L7" s="1" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="1" t="n"/>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="1" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="1" t="n"/>
       <c r="K9" s="8" t="n"/>
       <c r="L9" s="1" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="1" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="1" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Encourages formal procedure registration and ensures traceability.</t>
         </is>
@@ -1400,7 +1400,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session, which may cover several samples, and this is the link back to the raw instrument files.</t>
         </is>
@@ -1479,7 +1479,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="1" t="n"/>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="1" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="1" t="n"/>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="1" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="1" t="n"/>
       <c r="K15" s="8" t="n"/>
       <c r="L15" s="1" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="1" t="n"/>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="1" t="n"/>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="1" t="n"/>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>Provides a stable, citable link to the companion method independent of whether a dataset has been deposited.</t>
         </is>
@@ -2012,7 +2012,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="1" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>Used for discoverability and procedure matching, and because the material type constrains sample preparation, calibration and matrix-matching requirements.</t>
         </is>
@@ -2225,7 +2225,7 @@
           <t>defines: sample</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session and may cover several samples.</t>
         </is>
@@ -2308,7 +2308,7 @@
           <t>defines: sampling unit</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n"/>
+      <c r="J24" s="1" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="1" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n"/>
+      <c r="J25" s="1" t="n"/>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="1" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
+      <c r="J26" s="1" t="n"/>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n"/>
+      <c r="J27" s="1" t="n"/>
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
           <t>preparation step</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="1" t="inlineStr">
         <is>
           <t>For isotope-ratio work, complete matrix dissolution is required to avoid isotopic fractionation during partial dissolution.</t>
         </is>
@@ -2695,7 +2695,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="1" t="inlineStr">
         <is>
           <t>Vessel type constrains maximum temperature and pressure and determines suitability for refractory mineral dissolution (e.g., Parr bombs required for complete silicate digestion at high temperatures).</t>
         </is>
@@ -2778,7 +2778,7 @@
           <t>defines: preparation step</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n"/>
+      <c r="J30" s="1" t="n"/>
       <c r="K30" s="8" t="n"/>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
           <t>preparation step</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="1" t="n"/>
       <c r="K31" s="8" t="n"/>
       <c r="L31" s="1" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
           <t>preparation step</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n"/>
+      <c r="J32" s="1" t="n"/>
       <c r="K32" s="8" t="n"/>
       <c r="L32" s="1" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="1" t="inlineStr">
         <is>
           <t>Directly affects instrument response and ion transmission. Mismatched molarity introduces matrix-induced mass bias offsets.</t>
         </is>
@@ -3098,7 +3098,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="1" t="inlineStr">
         <is>
           <t>Used for yield calculations and concentration back-calculation.</t>
         </is>
@@ -3181,7 +3181,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="1" t="inlineStr">
         <is>
           <t>Separation may be required to remove matrix elements that cause variable mass bias, to eliminate isobaric interferences, or to isolate an element group before measurement (e.g., Fe and Cu–Zn for isotope dilution, Hf separation from REE, removal of Cr and Ni from Fe fractions). It is usually mandatory for isotope-ratio procedures and optional for concentration measurement.</t>
         </is>
@@ -3264,7 +3264,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr">
         <is>
           <t>Spiking before digestion corrects for isotopic fractionation during dissolution and column chemistry.</t>
         </is>
@@ -3398,7 +3398,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>Recording it as a controlled value lets procedures be found by vendor.</t>
         </is>
@@ -3481,7 +3481,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="n"/>
+      <c r="J39" s="1" t="n"/>
       <c r="K39" s="8" t="n"/>
       <c r="L39" s="1" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>Single-collector sector-field instruments use a magnetic sector combined with an electrostatic analyser to achieve high mass resolution through physical separation of ion beams.</t>
         </is>
@@ -3639,7 +3639,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>Supports traceability to instrument service records.</t>
         </is>
@@ -3722,7 +3722,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="n"/>
+      <c r="J42" s="1" t="n"/>
       <c r="K42" s="8" t="n"/>
       <c r="L42" s="1" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>Some SF-ICP-MS instruments offer multiple cone geometries that differ in aperture size and affect ion transmission efficiency and matrix tolerance.</t>
         </is>
@@ -3884,7 +3884,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="1" t="inlineStr">
         <is>
           <t>Nickel is standard for most aqueous and nitric matrices; platinum is used for HCl-rich, high-TDS or organic matrices for its greater corrosion resistance; aluminium is used in some laboratories for high-purity work or enhanced sensitivity.</t>
         </is>
@@ -3967,7 +3967,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>Affects ion transmission efficiency, oxide formation, and doubly-charged species production.</t>
         </is>
@@ -4050,7 +4050,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" s="1" t="inlineStr">
         <is>
           <t>Capacitively decouples the plasma from the load coil, reducing secondary discharge and improving ion extraction efficiency. Actively used as a design feature on Thermo Element 2 and Element XR instruments.</t>
         </is>
@@ -4133,7 +4133,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr">
         <is>
           <t>Sector-field instruments allow selection of low resolution (LR; m/Δm ≈ 300–400), medium resolution (MR; m/Δm ≈ 2500–5000), or high resolution (HR; m/Δm ≈ 10,000).</t>
         </is>
@@ -4212,7 +4212,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="1" t="inlineStr">
         <is>
           <t>SF-ICP-MS instruments typically use a single SEM. Some instruments (e.g., Thermo Element XR) support triple mode: pulse counting for low signals, analog for mid-range signals, and Faraday cup for high signals.</t>
         </is>
@@ -4295,7 +4295,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="1" t="inlineStr">
         <is>
           <t>Affects droplet size distribution and sample introduction efficiency.</t>
         </is>
@@ -4378,7 +4378,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="1" t="inlineStr">
         <is>
           <t>Chamber type and temperature control aerosol droplet size and the solvent vapor load reaching the plasma. In some procedures a spray chamber is placed downstream of a desolvating nebulizer to improve signal stability.</t>
         </is>
@@ -4461,7 +4461,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J51" s="1" t="inlineStr">
         <is>
           <t>Lowers oxide production rates and increases sensitivity, and is commonly used for low-abundance analytes or small sample sizes. Note the trade-off: desolvation can introduce additional instrumental mass bias instability relative to wet plasma introduction.</t>
         </is>
@@ -4544,7 +4544,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n"/>
+      <c r="J52" s="1" t="n"/>
       <c r="K52" s="8" t="n"/>
       <c r="L52" s="1" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J53" s="2" t="n"/>
+      <c r="J53" s="1" t="n"/>
       <c r="K53" s="8" t="n"/>
       <c r="L53" s="1" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J54" s="2" t="n"/>
+      <c r="J54" s="1" t="n"/>
       <c r="K54" s="8" t="n"/>
       <c r="L54" s="1" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr">
         <is>
           <t>Serves as the procedure-level declaration of measurement type, distinct from the mode flag columns, which state per-field applicability. Ensures every procedure record is self-describing and comparable across the library.</t>
         </is>
@@ -4911,7 +4911,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="1" t="inlineStr">
         <is>
           <t>Controls ionization efficiency and oxide production rates.</t>
         </is>
@@ -4994,7 +4994,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" s="1" t="inlineStr">
         <is>
           <t>Influences plasma temperature and oxide ion formation.</t>
         </is>
@@ -5077,7 +5077,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J59" s="2" t="n"/>
+      <c r="J59" s="1" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="1" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="1" t="inlineStr">
         <is>
           <t>Controls aerosol transport and strongly influences signal sensitivity and stability.</t>
         </is>
@@ -5239,7 +5239,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="1" t="inlineStr">
         <is>
           <t>Argon make-up is standard and maintains total gas delivery where the carrier flow alone is insufficient — downstream of an ablation cell, or of a desolvation system that has removed solvent load. Small nitrogen or hydrogen additions enhance sensitivity for some elements.</t>
         </is>
@@ -5322,7 +5322,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" s="1" t="inlineStr">
         <is>
           <t>Normal plasma (&gt;1000 W RF) is standard for most solution SF-ICP-MS analyses. Cool plasma (≤900 W RF) reduces argide-based interferences (e.g., 40Ar12C+ on 52Cr) at the cost of reduced sensitivity and ionization efficiency for most elements.</t>
         </is>
@@ -5405,7 +5405,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J63" s="2" t="n"/>
+      <c r="J63" s="1" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="1" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J64" s="2" t="n"/>
+      <c r="J64" s="1" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="1" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="1" t="inlineStr">
         <is>
           <t>Useful yield is the more comparable of the two wherever the amount of material consumed varies between procedures, as it does with spot size, fluence and repetition rate.</t>
         </is>
@@ -5642,7 +5642,7 @@
           <t>defines: analyte</t>
         </is>
       </c>
-      <c r="J66" s="2" t="n"/>
+      <c r="J66" s="1" t="n"/>
       <c r="K66" s="8" t="n"/>
       <c r="L66" s="1" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
           <t>defines: reported property</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J67" s="1" t="inlineStr">
         <is>
           <t>A procedure may acquire many channels and report a small number of derived quantities; without this field a data consumer cannot tell which.</t>
         </is>
@@ -5800,7 +5800,7 @@
           <t>defines: channel per analyte</t>
         </is>
       </c>
-      <c r="J68" s="2" t="n"/>
+      <c r="J68" s="1" t="n"/>
       <c r="K68" s="8" t="n"/>
       <c r="L68" s="1" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J69" s="1" t="inlineStr">
         <is>
           <t>The selected resolution determines which polyatomic interferences are physically resolved by the magnetic sector.</t>
         </is>
@@ -5954,7 +5954,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J70" s="1" t="inlineStr">
         <is>
           <t>Varies the accelerating voltage to cover masses in the vicinity of the set magnetic mass without re-scanning the magnet.</t>
         </is>
@@ -6033,7 +6033,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J71" s="1" t="inlineStr">
         <is>
           <t>Used to reduce noise from short-term magnetic field instabilities on sector-field instruments. Triple scanning affects the effective integration time per cycle.</t>
         </is>
@@ -6108,7 +6108,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J72" s="2" t="n"/>
+      <c r="J72" s="1" t="n"/>
       <c r="K72" s="8" t="n"/>
       <c r="L72" s="1" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J73" s="2" t="n"/>
+      <c r="J73" s="1" t="n"/>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="1" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J74" s="2" t="n"/>
+      <c r="J74" s="1" t="n"/>
       <c r="K74" s="8" t="n"/>
       <c r="L74" s="1" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J75" s="2" t="n"/>
+      <c r="J75" s="1" t="n"/>
       <c r="K75" s="8" t="n"/>
       <c r="L75" s="1" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J76" s="1" t="inlineStr">
         <is>
           <t>Controls carryover and memory effects. For isotope-ratio work, complete washout is critical to prevent cross-contamination between samples with differing isotopic compositions.</t>
         </is>
@@ -6499,7 +6499,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J77" s="2" t="n"/>
+      <c r="J77" s="1" t="n"/>
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="1" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J78" s="2" t="n"/>
+      <c r="J78" s="1" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="1" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J79" s="1" t="inlineStr">
         <is>
           <t>Stricter thresholds than Q-ICP-MS are commonly required.</t>
         </is>
@@ -6740,7 +6740,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J80" s="2" t="n"/>
+      <c r="J80" s="1" t="n"/>
       <c r="K80" s="8" t="n"/>
       <c r="L80" s="1" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J81" s="1" t="inlineStr">
         <is>
           <t>Doubly-charged ions appear at half the nominal mass of the parent ion and can interfere with lighter analyte masses. In SF-ICP-MS, doubly-charged species are not suppressed by collision cells and require monitoring through plasma tuning. Ba2+/Ba+ (m/z 69/138) is the most common proxy.</t>
         </is>
@@ -6894,7 +6894,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="J82" s="1" t="inlineStr">
         <is>
           <t>Elevated doubly-charged production indicates incomplete ionization and potential interference on elements at approximately half the mass of abundant matrix components.</t>
         </is>
@@ -6977,7 +6977,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J83" s="2" t="n"/>
+      <c r="J83" s="1" t="n"/>
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="1" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J85" s="2" t="n"/>
+      <c r="J85" s="1" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="1" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
           <t>analyte</t>
         </is>
       </c>
-      <c r="J86" s="2" t="n"/>
+      <c r="J86" s="1" t="n"/>
       <c r="K86" s="8" t="n"/>
       <c r="L86" s="1" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J87" s="2" t="n"/>
+      <c r="J87" s="1" t="n"/>
       <c r="K87" s="8" t="n"/>
       <c r="L87" s="1" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J88" s="2" t="n"/>
+      <c r="J88" s="1" t="n"/>
       <c r="K88" s="8" t="n"/>
       <c r="L88" s="1" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J89" s="2" t="n"/>
+      <c r="J89" s="1" t="n"/>
       <c r="K89" s="8" t="n"/>
       <c r="L89" s="1" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J90" s="2" t="n"/>
+      <c r="J90" s="1" t="n"/>
       <c r="K90" s="8" t="n"/>
       <c r="L90" s="1" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J91" s="1" t="inlineStr">
         <is>
           <t>For SF-ICP-MS instruments, the signal transitions between pulse counting (low concentrations) and analog detection (high concentrations). For triple-mode instruments (e.g., Thermo Element XR), an additional transition to Faraday cup detection occurs at the highest signal intensities.</t>
         </is>
@@ -7656,7 +7656,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J92" s="2" t="n"/>
+      <c r="J92" s="1" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="1" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J93" s="1" t="inlineStr">
         <is>
           <t>In SF-ICP-MS, mass resolution is the primary interference mitigation strategy; mathematical corrections address residual interferences not resolved at the operating resolution.</t>
         </is>
@@ -7818,7 +7818,7 @@
           <t>channel</t>
         </is>
       </c>
-      <c r="J94" s="2" t="n"/>
+      <c r="J94" s="1" t="n"/>
       <c r="K94" s="8" t="n"/>
       <c r="L94" s="1" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J95" s="2" t="n"/>
+      <c r="J95" s="1" t="n"/>
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="1" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J96" s="2" t="n"/>
+      <c r="J96" s="1" t="n"/>
       <c r="K96" s="8" t="n"/>
       <c r="L96" s="1" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="J97" s="1" t="inlineStr">
         <is>
           <t>A reported uncertainty is not interpretable without it: the same numeric value means different things at 1-sigma and at 95% confidence.</t>
         </is>
@@ -8138,7 +8138,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J98" s="2" t="n"/>
+      <c r="J98" s="1" t="n"/>
       <c r="K98" s="8" t="n"/>
       <c r="L98" s="1" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J99" s="2" t="n"/>
+      <c r="J99" s="1" t="n"/>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="1" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J100" s="2" t="n"/>
+      <c r="J100" s="1" t="n"/>
       <c r="K100" s="8" t="n"/>
       <c r="L100" s="1" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
           <t>analyte</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="J101" s="1" t="inlineStr">
         <is>
           <t>Follows the criterion-versus-measurement split the library applies wherever a procedure sets a threshold and an analysis reports a value against it.</t>
         </is>
@@ -8446,7 +8446,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="J102" s="1" t="inlineStr">
         <is>
           <t>Criteria and outcome are combined in one field because neither is interpretable without the other, following the precision/accuracy precedent.</t>
         </is>
@@ -8529,7 +8529,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J103" s="2" t="n"/>
+      <c r="J103" s="1" t="n"/>
       <c r="K103" s="8" t="n"/>
       <c r="L103" s="1" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
           <t>analyte</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J105" s="1" t="inlineStr">
         <is>
           <t>Results calibrated against different published values for the same material are not directly comparable.</t>
         </is>
@@ -8746,7 +8746,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J106" s="2" t="n"/>
+      <c r="J106" s="1" t="n"/>
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="1" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
           <t>defines: standard</t>
         </is>
       </c>
-      <c r="J107" s="2" t="n"/>
+      <c r="J107" s="1" t="n"/>
       <c r="K107" s="8" t="n"/>
       <c r="L107" s="1" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J108" s="2" t="n"/>
+      <c r="J108" s="1" t="n"/>
       <c r="K108" s="8" t="n"/>
       <c r="L108" s="1" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J109" s="2" t="n"/>
+      <c r="J109" s="1" t="n"/>
       <c r="K109" s="8" t="n"/>
       <c r="L109" s="1" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J110" s="2" t="n"/>
+      <c r="J110" s="1" t="n"/>
       <c r="K110" s="8" t="n"/>
       <c r="L110" s="1" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
           <t>sample &gt; sampling unit x reported property</t>
         </is>
       </c>
-      <c r="J111" s="2" t="inlineStr">
+      <c r="J111" s="1" t="inlineStr">
         <is>
           <t>Where a procedure reports both, agreement indicates the measurement is shot-noise limited, and a larger observed scatter indicates a further source of variance.</t>
         </is>
@@ -9220,7 +9220,7 @@
           <t>sample &gt; sampling unit x reported property</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="J112" s="1" t="inlineStr">
         <is>
           <t>This is the finest of the three precision levels the library records, below within-session and between-session precision: it describes the repeatability of one analysis rather than agreement between analyses, and is normally the smallest of the three.</t>
         </is>
@@ -9303,7 +9303,7 @@
           <t>standard x reported property</t>
         </is>
       </c>
-      <c r="J113" s="2" t="n"/>
+      <c r="J113" s="1" t="n"/>
       <c r="K113" s="8" t="n"/>
       <c r="L113" s="1" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
           <t>standard x reported property</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J114" s="1" t="inlineStr">
         <is>
           <t>Long-term precision is normally poorer than within-session precision and is the figure a data user should carry when comparing results from different sessions.</t>
         </is>
@@ -9465,7 +9465,7 @@
           <t>standard x reported property</t>
         </is>
       </c>
-      <c r="J115" s="2" t="n"/>
+      <c r="J115" s="1" t="n"/>
       <c r="K115" s="8" t="n"/>
       <c r="L115" s="1" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr">
+      <c r="J116" s="1" t="inlineStr">
         <is>
           <t>Answers whether a reported aggregate is defensible as a single population. The value cannot be known before the analysis.</t>
         </is>
@@ -9619,7 +9619,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J117" s="2" t="n"/>
+      <c r="J117" s="1" t="n"/>
       <c r="K117" s="8" t="n"/>
       <c r="L117" s="1" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9785,304 +9785,296 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n"/>
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>This field applies to this analytical mode and should be reported.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>This field applies to this analytical mode and should be reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
           <t>This field does not apply to this analytical mode.</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>What to enter</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>What to enter</t>
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Controlled list</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>Controlled list</t>
+          <t>Controlled list / Text</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
+          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>Controlled list / Text</t>
+          <t>Numeric (unit)</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
+          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>Numeric (unit)</t>
+          <t>Numeric + unit</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
+          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
         <is>
-          <t>Numeric + unit</t>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
+          <t>Free text. No controlled vocabulary applies.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>Text (free)</t>
+          <t>N/A | None</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Free text. No controlled vocabulary applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>N/A | None</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
           <t>Offered by every controlled list. "N/A" means the field does not apply to this procedure; "None" means it applies but nothing was used. Prefer either over leaving the cell blank.</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Keyed By (Rule 7)</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>What the field's value repeats over</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Keyed By (Rule 7)</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>What the field's value repeats over</t>
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>Scalar — one value per procedure or analysis. The default.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>analyte</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Scalar — one value per procedure or analysis. The default.</t>
+          <t>One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>analyte</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>One value per chemical species determined, at whatever granularity the procedure determines it.</t>
+          <t>One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>defines: analyte</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>defines: analyte</t>
+          <t>defines: channel per analyte</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
+          <t>ENUMERATES the channel domain — the header of the child table, not a column in it — and does so once per analyte. One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>defines: channel per analyte</t>
+          <t>defines: preparation step</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the channel domain — the header of the child table, not a column in it — and does so once per analyte. One value per position on the instrument's selection axis — the address, not the signal. Mass, cup, line + crystal, energy-loss edge, wavenumber. One value per chemical species determined, at whatever granularity the procedure determines it.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per stage in sample preparation.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>defines: preparation step</t>
+          <t>defines: reported property</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per stage in sample preparation.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>defines: reported property</t>
+          <t>defines: sample</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
+          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>defines: sample</t>
+          <t>defines: sampling unit</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>defines: sampling unit</t>
+          <t>defines: standard</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reference material or reference database entry.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>defines: standard</t>
+          <t>preparation step</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reference material or reference database entry.</t>
+          <t>One value per stage in sample preparation.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>preparation step</t>
+          <t>reported property</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>One value per stage in sample preparation.</t>
+          <t>One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>reported property</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
-        </is>
-      </c>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr"/>
+          <t>sample &gt; sampling unit x reported property</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>Cross-product, read as "for each sample, one value per reported property". One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume. + One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>sample &gt; sampling unit x reported property</t>
+          <t>standard x reported property</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>Cross-product, read as "for each sample, one value per reported property". One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume. + One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>standard x reported property</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>Cross-product, read as "for each standard, one value per reported property". One value per reference material or reference database entry. + One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
